--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H168"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5122,6 +5122,34 @@
         <v>35</v>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>6</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" t="n">
+        <v>86</v>
+      </c>
+      <c r="E169" t="n">
+        <v>39</v>
+      </c>
+      <c r="F169" t="n">
+        <v>48</v>
+      </c>
+      <c r="G169" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" t="n">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5150,6 +5150,34 @@
         <v>35</v>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>6</v>
+      </c>
+      <c r="C170" t="n">
+        <v>1</v>
+      </c>
+      <c r="D170" t="n">
+        <v>89</v>
+      </c>
+      <c r="E170" t="n">
+        <v>40</v>
+      </c>
+      <c r="F170" t="n">
+        <v>48</v>
+      </c>
+      <c r="G170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" t="n">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:H171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5178,6 +5178,34 @@
         <v>35</v>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>17</v>
+      </c>
+      <c r="C171" t="n">
+        <v>2</v>
+      </c>
+      <c r="D171" t="n">
+        <v>102</v>
+      </c>
+      <c r="E171" t="n">
+        <v>44</v>
+      </c>
+      <c r="F171" t="n">
+        <v>49</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="n">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H171"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5206,6 +5206,34 @@
         <v>35</v>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>17</v>
+      </c>
+      <c r="C172" t="n">
+        <v>2</v>
+      </c>
+      <c r="D172" t="n">
+        <v>101</v>
+      </c>
+      <c r="E172" t="n">
+        <v>42</v>
+      </c>
+      <c r="F172" t="n">
+        <v>50</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="n">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H172"/>
+  <dimension ref="A1:H173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5234,6 +5234,34 @@
         <v>35</v>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>17</v>
+      </c>
+      <c r="C173" t="n">
+        <v>2</v>
+      </c>
+      <c r="D173" t="n">
+        <v>102</v>
+      </c>
+      <c r="E173" t="n">
+        <v>42</v>
+      </c>
+      <c r="F173" t="n">
+        <v>50</v>
+      </c>
+      <c r="G173" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" t="n">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H173"/>
+  <dimension ref="A1:H174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5262,6 +5262,34 @@
         <v>35</v>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>17</v>
+      </c>
+      <c r="C174" t="n">
+        <v>2</v>
+      </c>
+      <c r="D174" t="n">
+        <v>126</v>
+      </c>
+      <c r="E174" t="n">
+        <v>56</v>
+      </c>
+      <c r="F174" t="n">
+        <v>50</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" t="n">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H174"/>
+  <dimension ref="A1:H175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5290,6 +5290,34 @@
         <v>35</v>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>17</v>
+      </c>
+      <c r="C175" t="n">
+        <v>2</v>
+      </c>
+      <c r="D175" t="n">
+        <v>132</v>
+      </c>
+      <c r="E175" t="n">
+        <v>60</v>
+      </c>
+      <c r="F175" t="n">
+        <v>50</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="n">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5318,6 +5318,34 @@
         <v>35</v>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>17</v>
+      </c>
+      <c r="C176" t="n">
+        <v>2</v>
+      </c>
+      <c r="D176" t="n">
+        <v>132</v>
+      </c>
+      <c r="E176" t="n">
+        <v>59</v>
+      </c>
+      <c r="F176" t="n">
+        <v>51</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="n">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H176"/>
+  <dimension ref="A1:H177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5346,6 +5346,34 @@
         <v>35</v>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>17</v>
+      </c>
+      <c r="C177" t="n">
+        <v>2</v>
+      </c>
+      <c r="D177" t="n">
+        <v>122</v>
+      </c>
+      <c r="E177" t="n">
+        <v>52</v>
+      </c>
+      <c r="F177" t="n">
+        <v>51</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" t="n">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5374,6 +5374,34 @@
         <v>35</v>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>18</v>
+      </c>
+      <c r="C178" t="n">
+        <v>3</v>
+      </c>
+      <c r="D178" t="n">
+        <v>115</v>
+      </c>
+      <c r="E178" t="n">
+        <v>51</v>
+      </c>
+      <c r="F178" t="n">
+        <v>52</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" t="n">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H178"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5402,6 +5402,34 @@
         <v>35</v>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>12</v>
+      </c>
+      <c r="C179" t="n">
+        <v>2</v>
+      </c>
+      <c r="D179" t="n">
+        <v>125</v>
+      </c>
+      <c r="E179" t="n">
+        <v>57</v>
+      </c>
+      <c r="F179" t="n">
+        <v>53</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" t="n">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H179"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5430,6 +5430,34 @@
         <v>35</v>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>13</v>
+      </c>
+      <c r="C180" t="n">
+        <v>2</v>
+      </c>
+      <c r="D180" t="n">
+        <v>128</v>
+      </c>
+      <c r="E180" t="n">
+        <v>58</v>
+      </c>
+      <c r="F180" t="n">
+        <v>53</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" t="n">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H180"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5458,6 +5458,34 @@
         <v>35</v>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>13</v>
+      </c>
+      <c r="C181" t="n">
+        <v>2</v>
+      </c>
+      <c r="D181" t="n">
+        <v>128</v>
+      </c>
+      <c r="E181" t="n">
+        <v>58</v>
+      </c>
+      <c r="F181" t="n">
+        <v>53</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" t="n">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H181"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5486,6 +5486,34 @@
         <v>35</v>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>13</v>
+      </c>
+      <c r="C182" t="n">
+        <v>2</v>
+      </c>
+      <c r="D182" t="n">
+        <v>128</v>
+      </c>
+      <c r="E182" t="n">
+        <v>58</v>
+      </c>
+      <c r="F182" t="n">
+        <v>53</v>
+      </c>
+      <c r="G182" t="n">
+        <v>1</v>
+      </c>
+      <c r="H182" t="n">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5514,6 +5514,34 @@
         <v>35</v>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>13</v>
+      </c>
+      <c r="C183" t="n">
+        <v>2</v>
+      </c>
+      <c r="D183" t="n">
+        <v>128</v>
+      </c>
+      <c r="E183" t="n">
+        <v>58</v>
+      </c>
+      <c r="F183" t="n">
+        <v>53</v>
+      </c>
+      <c r="G183" t="n">
+        <v>1</v>
+      </c>
+      <c r="H183" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H183"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5542,6 +5542,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>13</v>
+      </c>
+      <c r="C184" t="n">
+        <v>2</v>
+      </c>
+      <c r="D184" t="n">
+        <v>128</v>
+      </c>
+      <c r="E184" t="n">
+        <v>58</v>
+      </c>
+      <c r="F184" t="n">
+        <v>53</v>
+      </c>
+      <c r="G184" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:H185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5570,6 +5570,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>3</v>
+      </c>
+      <c r="C185" t="n">
+        <v>2</v>
+      </c>
+      <c r="D185" t="n">
+        <v>133</v>
+      </c>
+      <c r="E185" t="n">
+        <v>61</v>
+      </c>
+      <c r="F185" t="n">
+        <v>53</v>
+      </c>
+      <c r="G185" t="n">
+        <v>1</v>
+      </c>
+      <c r="H185" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5598,6 +5598,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>4</v>
+      </c>
+      <c r="C186" t="n">
+        <v>3</v>
+      </c>
+      <c r="D186" t="n">
+        <v>131</v>
+      </c>
+      <c r="E186" t="n">
+        <v>60</v>
+      </c>
+      <c r="F186" t="n">
+        <v>53</v>
+      </c>
+      <c r="G186" t="n">
+        <v>1</v>
+      </c>
+      <c r="H186" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5626,6 +5626,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>4</v>
+      </c>
+      <c r="C187" t="n">
+        <v>3</v>
+      </c>
+      <c r="D187" t="n">
+        <v>143</v>
+      </c>
+      <c r="E187" t="n">
+        <v>68</v>
+      </c>
+      <c r="F187" t="n">
+        <v>53</v>
+      </c>
+      <c r="G187" t="n">
+        <v>1</v>
+      </c>
+      <c r="H187" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H187"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5654,6 +5654,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>4</v>
+      </c>
+      <c r="C188" t="n">
+        <v>3</v>
+      </c>
+      <c r="D188" t="n">
+        <v>124</v>
+      </c>
+      <c r="E188" t="n">
+        <v>58</v>
+      </c>
+      <c r="F188" t="n">
+        <v>54</v>
+      </c>
+      <c r="G188" t="n">
+        <v>5</v>
+      </c>
+      <c r="H188" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5682,6 +5682,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>4</v>
+      </c>
+      <c r="C189" t="n">
+        <v>3</v>
+      </c>
+      <c r="D189" t="n">
+        <v>134</v>
+      </c>
+      <c r="E189" t="n">
+        <v>64</v>
+      </c>
+      <c r="F189" t="n">
+        <v>54</v>
+      </c>
+      <c r="G189" t="n">
+        <v>6</v>
+      </c>
+      <c r="H189" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H189"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5710,6 +5710,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>4</v>
+      </c>
+      <c r="C190" t="n">
+        <v>3</v>
+      </c>
+      <c r="D190" t="n">
+        <v>134</v>
+      </c>
+      <c r="E190" t="n">
+        <v>65</v>
+      </c>
+      <c r="F190" t="n">
+        <v>54</v>
+      </c>
+      <c r="G190" t="n">
+        <v>6</v>
+      </c>
+      <c r="H190" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5738,6 +5738,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>4</v>
+      </c>
+      <c r="C191" t="n">
+        <v>3</v>
+      </c>
+      <c r="D191" t="n">
+        <v>136</v>
+      </c>
+      <c r="E191" t="n">
+        <v>66</v>
+      </c>
+      <c r="F191" t="n">
+        <v>54</v>
+      </c>
+      <c r="G191" t="n">
+        <v>6</v>
+      </c>
+      <c r="H191" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H191"/>
+  <dimension ref="A1:H192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5766,6 +5766,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>3</v>
+      </c>
+      <c r="C192" t="n">
+        <v>2</v>
+      </c>
+      <c r="D192" t="n">
+        <v>141</v>
+      </c>
+      <c r="E192" t="n">
+        <v>69</v>
+      </c>
+      <c r="F192" t="n">
+        <v>54</v>
+      </c>
+      <c r="G192" t="n">
+        <v>6</v>
+      </c>
+      <c r="H192" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H192"/>
+  <dimension ref="A1:H193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5794,6 +5794,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>3</v>
+      </c>
+      <c r="C193" t="n">
+        <v>2</v>
+      </c>
+      <c r="D193" t="n">
+        <v>130</v>
+      </c>
+      <c r="E193" t="n">
+        <v>64</v>
+      </c>
+      <c r="F193" t="n">
+        <v>54</v>
+      </c>
+      <c r="G193" t="n">
+        <v>6</v>
+      </c>
+      <c r="H193" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H193"/>
+  <dimension ref="A1:H194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5822,6 +5822,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>2</v>
+      </c>
+      <c r="C194" t="n">
+        <v>2</v>
+      </c>
+      <c r="D194" t="n">
+        <v>137</v>
+      </c>
+      <c r="E194" t="n">
+        <v>68</v>
+      </c>
+      <c r="F194" t="n">
+        <v>54</v>
+      </c>
+      <c r="G194" t="n">
+        <v>6</v>
+      </c>
+      <c r="H194" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H194"/>
+  <dimension ref="A1:H195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5850,6 +5850,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>1</v>
+      </c>
+      <c r="C195" t="n">
+        <v>1</v>
+      </c>
+      <c r="D195" t="n">
+        <v>125</v>
+      </c>
+      <c r="E195" t="n">
+        <v>60</v>
+      </c>
+      <c r="F195" t="n">
+        <v>54</v>
+      </c>
+      <c r="G195" t="n">
+        <v>6</v>
+      </c>
+      <c r="H195" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H195"/>
+  <dimension ref="A1:H196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5878,6 +5878,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>1</v>
+      </c>
+      <c r="C196" t="n">
+        <v>1</v>
+      </c>
+      <c r="D196" t="n">
+        <v>137</v>
+      </c>
+      <c r="E196" t="n">
+        <v>66</v>
+      </c>
+      <c r="F196" t="n">
+        <v>54</v>
+      </c>
+      <c r="G196" t="n">
+        <v>6</v>
+      </c>
+      <c r="H196" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H196"/>
+  <dimension ref="A1:H197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5906,6 +5906,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>1</v>
+      </c>
+      <c r="C197" t="n">
+        <v>1</v>
+      </c>
+      <c r="D197" t="n">
+        <v>139</v>
+      </c>
+      <c r="E197" t="n">
+        <v>67</v>
+      </c>
+      <c r="F197" t="n">
+        <v>54</v>
+      </c>
+      <c r="G197" t="n">
+        <v>6</v>
+      </c>
+      <c r="H197" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H197"/>
+  <dimension ref="A1:H198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5934,6 +5934,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1</v>
+      </c>
+      <c r="C198" t="n">
+        <v>1</v>
+      </c>
+      <c r="D198" t="n">
+        <v>157</v>
+      </c>
+      <c r="E198" t="n">
+        <v>77</v>
+      </c>
+      <c r="F198" t="n">
+        <v>54</v>
+      </c>
+      <c r="G198" t="n">
+        <v>9</v>
+      </c>
+      <c r="H198" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H198"/>
+  <dimension ref="A1:H199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5962,6 +5962,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>1</v>
+      </c>
+      <c r="C199" t="n">
+        <v>1</v>
+      </c>
+      <c r="D199" t="n">
+        <v>156</v>
+      </c>
+      <c r="E199" t="n">
+        <v>75</v>
+      </c>
+      <c r="F199" t="n">
+        <v>54</v>
+      </c>
+      <c r="G199" t="n">
+        <v>9</v>
+      </c>
+      <c r="H199" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H199"/>
+  <dimension ref="A1:H200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5990,6 +5990,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>0</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0</v>
+      </c>
+      <c r="D200" t="n">
+        <v>155</v>
+      </c>
+      <c r="E200" t="n">
+        <v>76</v>
+      </c>
+      <c r="F200" t="n">
+        <v>54</v>
+      </c>
+      <c r="G200" t="n">
+        <v>11</v>
+      </c>
+      <c r="H200" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H200"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6018,6 +6018,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>0</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0</v>
+      </c>
+      <c r="D201" t="n">
+        <v>157</v>
+      </c>
+      <c r="E201" t="n">
+        <v>74</v>
+      </c>
+      <c r="F201" t="n">
+        <v>55</v>
+      </c>
+      <c r="G201" t="n">
+        <v>13</v>
+      </c>
+      <c r="H201" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H201"/>
+  <dimension ref="A1:H202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6046,6 +6046,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>0</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0</v>
+      </c>
+      <c r="D202" t="n">
+        <v>138</v>
+      </c>
+      <c r="E202" t="n">
+        <v>64</v>
+      </c>
+      <c r="F202" t="n">
+        <v>55</v>
+      </c>
+      <c r="G202" t="n">
+        <v>15</v>
+      </c>
+      <c r="H202" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H202"/>
+  <dimension ref="A1:H203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6074,6 +6074,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>0</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0</v>
+      </c>
+      <c r="D203" t="n">
+        <v>138</v>
+      </c>
+      <c r="E203" t="n">
+        <v>64</v>
+      </c>
+      <c r="F203" t="n">
+        <v>55</v>
+      </c>
+      <c r="G203" t="n">
+        <v>16</v>
+      </c>
+      <c r="H203" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H203"/>
+  <dimension ref="A1:H204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6102,6 +6102,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>0</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0</v>
+      </c>
+      <c r="D204" t="n">
+        <v>147</v>
+      </c>
+      <c r="E204" t="n">
+        <v>67</v>
+      </c>
+      <c r="F204" t="n">
+        <v>55</v>
+      </c>
+      <c r="G204" t="n">
+        <v>16</v>
+      </c>
+      <c r="H204" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H204"/>
+  <dimension ref="A1:H205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6130,6 +6130,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>0</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0</v>
+      </c>
+      <c r="D205" t="n">
+        <v>154</v>
+      </c>
+      <c r="E205" t="n">
+        <v>70</v>
+      </c>
+      <c r="F205" t="n">
+        <v>55</v>
+      </c>
+      <c r="G205" t="n">
+        <v>16</v>
+      </c>
+      <c r="H205" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H205"/>
+  <dimension ref="A1:H206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6158,6 +6158,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>0</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0</v>
+      </c>
+      <c r="D206" t="n">
+        <v>156</v>
+      </c>
+      <c r="E206" t="n">
+        <v>72</v>
+      </c>
+      <c r="F206" t="n">
+        <v>56</v>
+      </c>
+      <c r="G206" t="n">
+        <v>16</v>
+      </c>
+      <c r="H206" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H206"/>
+  <dimension ref="A1:H207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6186,6 +6186,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>0</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0</v>
+      </c>
+      <c r="D207" t="n">
+        <v>150</v>
+      </c>
+      <c r="E207" t="n">
+        <v>68</v>
+      </c>
+      <c r="F207" t="n">
+        <v>57</v>
+      </c>
+      <c r="G207" t="n">
+        <v>16</v>
+      </c>
+      <c r="H207" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H207"/>
+  <dimension ref="A1:H208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6214,6 +6214,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>0</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" t="n">
+        <v>153</v>
+      </c>
+      <c r="E208" t="n">
+        <v>71</v>
+      </c>
+      <c r="F208" t="n">
+        <v>57</v>
+      </c>
+      <c r="G208" t="n">
+        <v>17</v>
+      </c>
+      <c r="H208" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H208"/>
+  <dimension ref="A1:H209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6242,6 +6242,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>0</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0</v>
+      </c>
+      <c r="D209" t="n">
+        <v>149</v>
+      </c>
+      <c r="E209" t="n">
+        <v>69</v>
+      </c>
+      <c r="F209" t="n">
+        <v>57</v>
+      </c>
+      <c r="G209" t="n">
+        <v>22</v>
+      </c>
+      <c r="H209" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H209"/>
+  <dimension ref="A1:H210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6270,6 +6270,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>1</v>
+      </c>
+      <c r="C210" t="n">
+        <v>1</v>
+      </c>
+      <c r="D210" t="n">
+        <v>171</v>
+      </c>
+      <c r="E210" t="n">
+        <v>78</v>
+      </c>
+      <c r="F210" t="n">
+        <v>57</v>
+      </c>
+      <c r="G210" t="n">
+        <v>22</v>
+      </c>
+      <c r="H210" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H210"/>
+  <dimension ref="A1:H211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6298,6 +6298,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>1</v>
+      </c>
+      <c r="C211" t="n">
+        <v>1</v>
+      </c>
+      <c r="D211" t="n">
+        <v>151</v>
+      </c>
+      <c r="E211" t="n">
+        <v>68</v>
+      </c>
+      <c r="F211" t="n">
+        <v>57</v>
+      </c>
+      <c r="G211" t="n">
+        <v>27</v>
+      </c>
+      <c r="H211" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H211"/>
+  <dimension ref="A1:H212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6326,6 +6326,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>1</v>
+      </c>
+      <c r="C212" t="n">
+        <v>1</v>
+      </c>
+      <c r="D212" t="n">
+        <v>155</v>
+      </c>
+      <c r="E212" t="n">
+        <v>64</v>
+      </c>
+      <c r="F212" t="n">
+        <v>57</v>
+      </c>
+      <c r="G212" t="n">
+        <v>27</v>
+      </c>
+      <c r="H212" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H212"/>
+  <dimension ref="A1:H213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6354,6 +6354,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>1</v>
+      </c>
+      <c r="C213" t="n">
+        <v>1</v>
+      </c>
+      <c r="D213" t="n">
+        <v>156</v>
+      </c>
+      <c r="E213" t="n">
+        <v>65</v>
+      </c>
+      <c r="F213" t="n">
+        <v>57</v>
+      </c>
+      <c r="G213" t="n">
+        <v>28</v>
+      </c>
+      <c r="H213" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H213"/>
+  <dimension ref="A1:H214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6382,6 +6382,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>1</v>
+      </c>
+      <c r="C214" t="n">
+        <v>1</v>
+      </c>
+      <c r="D214" t="n">
+        <v>158</v>
+      </c>
+      <c r="E214" t="n">
+        <v>67</v>
+      </c>
+      <c r="F214" t="n">
+        <v>57</v>
+      </c>
+      <c r="G214" t="n">
+        <v>28</v>
+      </c>
+      <c r="H214" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/github_traffic_log.xlsx
+++ b/github_traffic_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H214"/>
+  <dimension ref="A1:H215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6410,6 +6410,34 @@
         <v>36</v>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>2</v>
+      </c>
+      <c r="C215" t="n">
+        <v>2</v>
+      </c>
+      <c r="D215" t="n">
+        <v>137</v>
+      </c>
+      <c r="E215" t="n">
+        <v>58</v>
+      </c>
+      <c r="F215" t="n">
+        <v>58</v>
+      </c>
+      <c r="G215" t="n">
+        <v>28</v>
+      </c>
+      <c r="H215" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
